--- a/Figures.out/dat.out.xlsx
+++ b/Figures.out/dat.out.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">species</t>
   </si>
@@ -41,16 +41,34 @@
     <t xml:space="preserve">low</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96 ± 0.11</t>
+    <t xml:space="preserve">3.51 ± 0.77***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13 ± 0.28***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.31 ± 0.07***</t>
   </si>
   <si>
     <t xml:space="preserve">hi</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65 ± 0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28 ± 0.01</t>
+    <t xml:space="preserve">10.15 ± 2.73***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51 ± 0.11***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.24 ± 0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29 ± 0.13***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 ± 0.29***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.18 ± 0.01***</t>
   </si>
 </sst>
 </file>
@@ -424,19 +442,61 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="G3"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
